--- a/backend/Rwanda/capex-fuels-{model}.xlsx
+++ b/backend/Rwanda/capex-fuels-{model}.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC359ED6-CE3F-41CA-98C0-5AB0D7D5FDB8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="19">
   <si>
     <t>Units</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Total Annual Depreciation</t>
   </si>
   <si>
-    <t>Growth Capex</t>
-  </si>
-  <si>
     <t>Acc. Growth CAPEX</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>Maintenance CAPEX</t>
   </si>
   <si>
-    <t>ACC. Growth CAPEX</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -91,6 +85,15 @@
   </si>
   <si>
     <t>OFF-GRID</t>
+  </si>
+  <si>
+    <t>Acc. Maintenance CAPEX</t>
+  </si>
+  <si>
+    <t>RAB</t>
+  </si>
+  <si>
+    <t>Growth CAPEX</t>
   </si>
 </sst>
 </file>
@@ -511,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4224F1-5D48-4FE4-980F-718DB45087F0}">
-  <dimension ref="A1:AR18"/>
+  <dimension ref="A1:AR20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="33.08984375" customWidth="1"/>
@@ -519,10 +522,10 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -653,10 +656,10 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -787,10 +790,10 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>2</v>
@@ -921,10 +924,10 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>2</v>
@@ -1055,10 +1058,10 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>2</v>
@@ -1189,7 +1192,7 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
@@ -1323,10 +1326,10 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
@@ -1457,7 +1460,7 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -1591,7 +1594,7 @@
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
@@ -1723,280 +1726,280 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="s">
+    <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
+        <v>0</v>
+      </c>
+      <c r="V10" s="7">
+        <v>0</v>
+      </c>
+      <c r="W10" s="7">
+        <v>0</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E11" s="5">
         <v>2021</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F11" s="5">
         <v>2022</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G11" s="5">
         <v>2023</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H11" s="5">
         <v>2024</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I11" s="5">
         <v>2025</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J11" s="5">
         <v>2026</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K11" s="5">
         <v>2027</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="5">
         <v>2028</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M11" s="5">
         <v>2029</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N11" s="5">
         <v>2030</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O11" s="5">
         <v>2031</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P11" s="5">
         <v>2032</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q11" s="5">
         <v>2033</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R11" s="5">
         <v>2034</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S11" s="5">
         <v>2035</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T11" s="5">
         <v>2036</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U11" s="5">
         <v>2037</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V11" s="5">
         <v>2038</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W11" s="5">
         <v>2039</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X11" s="5">
         <v>2040</v>
       </c>
-      <c r="Y10" s="5">
+      <c r="Y11" s="5">
         <v>2041</v>
       </c>
-      <c r="Z10" s="5">
+      <c r="Z11" s="5">
         <v>2042</v>
       </c>
-      <c r="AA10" s="5">
+      <c r="AA11" s="5">
         <v>2043</v>
       </c>
-      <c r="AB10" s="5">
+      <c r="AB11" s="5">
         <v>2044</v>
       </c>
-      <c r="AC10" s="5">
+      <c r="AC11" s="5">
         <v>2045</v>
       </c>
-      <c r="AD10" s="5">
+      <c r="AD11" s="5">
         <v>2046</v>
       </c>
-      <c r="AE10" s="5">
+      <c r="AE11" s="5">
         <v>2047</v>
       </c>
-      <c r="AF10" s="5">
+      <c r="AF11" s="5">
         <v>2048</v>
       </c>
-      <c r="AG10" s="5">
+      <c r="AG11" s="5">
         <v>2049</v>
       </c>
-      <c r="AH10" s="5">
+      <c r="AH11" s="5">
         <v>2050</v>
       </c>
-      <c r="AI10" s="5">
+      <c r="AI11" s="5">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="5">
+      <c r="AJ11" s="5">
         <v>2052</v>
       </c>
-      <c r="AK10" s="5">
+      <c r="AK11" s="5">
         <v>2053</v>
       </c>
-      <c r="AL10" s="5">
+      <c r="AL11" s="5">
         <v>2054</v>
       </c>
-      <c r="AM10" s="5">
+      <c r="AM11" s="5">
         <v>2055</v>
       </c>
-      <c r="AN10" s="5">
+      <c r="AN11" s="5">
         <v>2056</v>
       </c>
-      <c r="AO10" s="5">
+      <c r="AO11" s="5">
         <v>2057</v>
       </c>
-      <c r="AP10" s="5">
+      <c r="AP11" s="5">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="5">
+      <c r="AQ11" s="5">
         <v>2059</v>
       </c>
-      <c r="AR10" s="5">
+      <c r="AR11" s="5">
         <v>2060</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>0</v>
-      </c>
-      <c r="I11" s="7">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" s="7">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
-      </c>
-      <c r="S11" s="7">
-        <v>0</v>
-      </c>
-      <c r="T11" s="7">
-        <v>0</v>
-      </c>
-      <c r="U11" s="7">
-        <v>0</v>
-      </c>
-      <c r="V11" s="7">
-        <v>0</v>
-      </c>
-      <c r="W11" s="7">
-        <v>0</v>
-      </c>
-      <c r="X11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2</v>
@@ -2127,10 +2130,10 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>2</v>
@@ -2261,10 +2264,10 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2</v>
@@ -2395,10 +2398,10 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>2</v>
@@ -2529,10 +2532,10 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2</v>
@@ -2663,269 +2666,537 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="7">
         <v>0</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR17" s="8" t="s">
-        <v>3</v>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
+      <c r="S17" s="7">
+        <v>0</v>
+      </c>
+      <c r="T17" s="7">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7">
+        <v>0</v>
+      </c>
+      <c r="V17" s="7">
+        <v>0</v>
+      </c>
+      <c r="W17" s="7">
+        <v>0</v>
+      </c>
+      <c r="X17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR18" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0</v>
+      </c>
+      <c r="T19" s="7">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7">
+        <v>0</v>
+      </c>
+      <c r="V19" s="7">
+        <v>0</v>
+      </c>
+      <c r="W19" s="7">
+        <v>0</v>
+      </c>
+      <c r="X19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7">
-        <v>0</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
-        <v>0</v>
-      </c>
-      <c r="S18" s="7">
-        <v>0</v>
-      </c>
-      <c r="T18" s="7">
-        <v>0</v>
-      </c>
-      <c r="U18" s="7">
-        <v>0</v>
-      </c>
-      <c r="V18" s="7">
-        <v>0</v>
-      </c>
-      <c r="W18" s="7">
-        <v>0</v>
-      </c>
-      <c r="X18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="7">
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
+      </c>
+      <c r="S20" s="7">
+        <v>0</v>
+      </c>
+      <c r="T20" s="7">
+        <v>0</v>
+      </c>
+      <c r="U20" s="7">
+        <v>0</v>
+      </c>
+      <c r="V20" s="7">
+        <v>0</v>
+      </c>
+      <c r="W20" s="7">
+        <v>0</v>
+      </c>
+      <c r="X20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2937,7 +3208,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2946,7 +3217,7 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3077,7 +3348,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -3208,7 +3479,7 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>2</v>
@@ -3339,7 +3610,7 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
@@ -3470,7 +3741,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>2</v>
@@ -3732,7 +4003,7 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>2</v>
@@ -4120,6 +4391,137 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
+        <v>0</v>
+      </c>
+      <c r="V10" s="7">
+        <v>0</v>
+      </c>
+      <c r="W10" s="7">
+        <v>0</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="7">
         <v>0</v>
       </c>
     </row>

--- a/backend/Rwanda/capex-fuels-{model}.xlsx
+++ b/backend/Rwanda/capex-fuels-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC359ED6-CE3F-41CA-98C0-5AB0D7D5FDB8}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A398004B-E4FD-452E-ABB1-C757397FDE72}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="6" r:id="rId1"/>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="18">
   <si>
     <t>Units</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>M$</t>
@@ -522,16 +519,16 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>1</v>
+      <c r="D1" s="5">
+        <v>2020</v>
       </c>
       <c r="E1" s="5">
         <v>2021</v>
@@ -656,13 +653,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7">
         <v>0</v>
@@ -790,13 +787,13 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -924,13 +921,13 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="7">
         <v>0</v>
@@ -1058,13 +1055,13 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="7">
         <v>0</v>
@@ -1192,13 +1189,13 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7">
         <v>0</v>
@@ -1326,13 +1323,13 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="7">
         <v>0</v>
@@ -1460,147 +1457,147 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7">
         <v>0</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
@@ -1728,13 +1725,13 @@
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7">
         <v>0</v>
@@ -1862,16 +1859,16 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>1</v>
+      <c r="D11" s="5">
+        <v>2020</v>
       </c>
       <c r="E11" s="5">
         <v>2021</v>
@@ -1996,13 +1993,13 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
@@ -2130,13 +2127,13 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="7">
         <v>0</v>
@@ -2264,13 +2261,13 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7">
         <v>0</v>
@@ -2398,13 +2395,13 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="7">
         <v>0</v>
@@ -2532,13 +2529,13 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7">
         <v>0</v>
@@ -2666,13 +2663,13 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="7">
         <v>0</v>
@@ -2800,147 +2797,147 @@
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR18" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="7">
         <v>0</v>
@@ -3068,13 +3065,13 @@
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -3217,13 +3214,13 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
+      <c r="C1" s="5">
+        <v>2020</v>
       </c>
       <c r="D1" s="5">
         <v>2021</v>
@@ -3348,10 +3345,10 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -3479,10 +3476,10 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="7">
         <v>0</v>
@@ -3610,10 +3607,10 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="7">
         <v>0</v>
@@ -3741,10 +3738,10 @@
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7">
         <v>0</v>
@@ -3872,10 +3869,10 @@
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
@@ -4003,10 +4000,10 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7">
         <v>0</v>
@@ -4134,141 +4131,141 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="7">
         <v>0</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7">
         <v>0</v>
@@ -4396,10 +4393,10 @@
     </row>
     <row r="10" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7">
         <v>0</v>

--- a/backend/Rwanda/capex-fuels-{model}.xlsx
+++ b/backend/Rwanda/capex-fuels-{model}.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A398004B-E4FD-452E-ABB1-C757397FDE72}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48F305A-EE29-4672-8886-D4B7E42C5AFC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="6" r:id="rId1"/>
@@ -37,15 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="17">
   <si>
     <t>Units</t>
   </si>
   <si>
     <t>M$</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Total CAPEX</t>
@@ -201,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -222,10 +219,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -519,10 +512,10 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -652,11 +645,11 @@
       </c>
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>13</v>
+      <c r="A2" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1</v>
@@ -786,11 +779,11 @@
       </c>
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>13</v>
+      <c r="A3" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1</v>
@@ -920,11 +913,11 @@
       </c>
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>13</v>
+      <c r="A4" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1</v>
@@ -1054,11 +1047,11 @@
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>13</v>
+      <c r="A5" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>1</v>
@@ -1188,11 +1181,11 @@
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>13</v>
+      <c r="A6" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1</v>
@@ -1322,11 +1315,11 @@
       </c>
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>13</v>
+      <c r="A7" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>1</v>
@@ -1456,145 +1449,145 @@
       </c>
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>13</v>
+      <c r="A8" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="7">
         <v>0</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR8" s="8" t="s">
-        <v>2</v>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>13</v>
+      <c r="A9" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1</v>
@@ -1724,11 +1717,11 @@
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>13</v>
+      <c r="A10" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1</v>
@@ -1859,10 +1852,10 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>0</v>
@@ -1992,11 +1985,11 @@
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>14</v>
+      <c r="A12" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1</v>
@@ -2126,11 +2119,11 @@
       </c>
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>14</v>
+      <c r="A13" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1</v>
@@ -2260,11 +2253,11 @@
       </c>
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>14</v>
+      <c r="A14" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1</v>
@@ -2394,11 +2387,11 @@
       </c>
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1</v>
@@ -2528,11 +2521,11 @@
       </c>
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>14</v>
+      <c r="A16" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1</v>
@@ -2662,11 +2655,11 @@
       </c>
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>14</v>
+      <c r="A17" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1</v>
@@ -2796,145 +2789,145 @@
       </c>
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>14</v>
+      <c r="A18" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="T18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="V18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="W18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="X18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR18" s="8" t="s">
-        <v>2</v>
+      <c r="E18" s="7">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="T18" s="7">
+        <v>0</v>
+      </c>
+      <c r="U18" s="7">
+        <v>0</v>
+      </c>
+      <c r="V18" s="7">
+        <v>0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>0</v>
+      </c>
+      <c r="X18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>14</v>
+      <c r="A19" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1</v>
@@ -3064,11 +3057,11 @@
       </c>
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>14</v>
+      <c r="A20" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1</v>
@@ -3214,7 +3207,7 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3345,7 +3338,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -3476,7 +3469,7 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
@@ -3607,7 +3600,7 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>1</v>
@@ -3738,7 +3731,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>1</v>
@@ -3869,7 +3862,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>1</v>
@@ -4000,7 +3993,7 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>1</v>
@@ -4131,138 +4124,138 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="7">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ8" s="8" t="s">
-        <v>2</v>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>1</v>
@@ -4393,7 +4386,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>1</v>

--- a/backend/Rwanda/capex-fuels-{model}.xlsx
+++ b/backend/Rwanda/capex-fuels-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7748D7-F3D8-4A86-87D5-60B7B3A143AE}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{40E2BDE7-11A9-429F-9E0E-82D55F13BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEAF0D86-F0D0-4D94-B3DE-7E4904BE619D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="18">
   <si>
     <t>Units</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Growth CAPEX</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
 </sst>
 </file>
@@ -240,6 +243,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,7 +520,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -1853,7 +1860,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -3206,7 +3213,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -4546,7 +4553,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
